--- a/artfynd/A 56647-2025 artfynd.xlsx
+++ b/artfynd/A 56647-2025 artfynd.xlsx
@@ -781,7 +781,7 @@
         <v>130180056</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>130180057</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130180055</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130180053</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130180011</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>130180010</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>130180012</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>130180013</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>130180058</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>130180054</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 56647-2025 artfynd.xlsx
+++ b/artfynd/A 56647-2025 artfynd.xlsx
@@ -781,7 +781,7 @@
         <v>130180056</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>130180057</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130180055</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130180053</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>130180058</v>
       </c>
       <c r="B11" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>130180054</v>
       </c>
       <c r="B12" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 56647-2025 artfynd.xlsx
+++ b/artfynd/A 56647-2025 artfynd.xlsx
@@ -781,7 +781,7 @@
         <v>130180056</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>130180057</v>
       </c>
       <c r="B4" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130180055</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130180053</v>
       </c>
       <c r="B6" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130180011</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>130180010</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>130180012</v>
       </c>
       <c r="B9" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>130180013</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>130180058</v>
       </c>
       <c r="B11" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>130180054</v>
       </c>
       <c r="B12" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 56647-2025 artfynd.xlsx
+++ b/artfynd/A 56647-2025 artfynd.xlsx
@@ -781,7 +781,7 @@
         <v>130180056</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>130180057</v>
       </c>
       <c r="B4" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130180055</v>
       </c>
       <c r="B5" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>130180053</v>
       </c>
       <c r="B6" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130180011</v>
       </c>
       <c r="B7" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>130180010</v>
       </c>
       <c r="B8" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>130180012</v>
       </c>
       <c r="B9" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>130180013</v>
       </c>
       <c r="B10" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>130180058</v>
       </c>
       <c r="B11" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>130180054</v>
       </c>
       <c r="B12" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 56647-2025 artfynd.xlsx
+++ b/artfynd/A 56647-2025 artfynd.xlsx
@@ -2093,42 +2093,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133965183</v>
+        <v>133965075</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>101389</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2136,10 +2136,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490539</v>
+        <v>490371</v>
       </c>
       <c r="R14" t="n">
-        <v>7023187</v>
+        <v>7023521</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2181,12 +2181,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:53</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, några meter upp på en gran. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2195,37 +2190,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2243,10 +2214,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133965075</v>
+        <v>133965162</v>
       </c>
       <c r="B15" t="n">
-        <v>101389</v>
+        <v>99203</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2254,28 +2225,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -2286,10 +2257,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490371</v>
+        <v>490592</v>
       </c>
       <c r="R15" t="n">
-        <v>7023521</v>
+        <v>7023284</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2321,7 +2292,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2331,7 +2302,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2663,10 +2634,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133965162</v>
+        <v>133965173</v>
       </c>
       <c r="B18" t="n">
-        <v>99203</v>
+        <v>101389</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2674,28 +2645,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2706,10 +2677,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490592</v>
+        <v>490485</v>
       </c>
       <c r="R18" t="n">
-        <v>7023284</v>
+        <v>7023307</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2741,7 +2712,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2751,7 +2722,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2766,7 +2737,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2784,10 +2755,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133965129</v>
+        <v>133965073</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2795,31 +2766,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2827,10 +2793,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490383</v>
+        <v>490362</v>
       </c>
       <c r="R19" t="n">
-        <v>7023375</v>
+        <v>7023519</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2862,7 +2828,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2872,12 +2838,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en klen gran.</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2886,6 +2847,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2906,12 +2868,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2929,42 +2891,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133965173</v>
+        <v>133965133</v>
       </c>
       <c r="B20" t="n">
-        <v>101389</v>
+        <v>79359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2972,10 +2929,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490485</v>
+        <v>490446</v>
       </c>
       <c r="R20" t="n">
-        <v>7023307</v>
+        <v>7023313</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3007,7 +2964,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3017,7 +2974,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3032,7 +2989,27 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3050,7 +3027,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133965073</v>
+        <v>133965159</v>
       </c>
       <c r="B21" t="n">
         <v>79359</v>
@@ -3088,10 +3065,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490362</v>
+        <v>490533</v>
       </c>
       <c r="R21" t="n">
-        <v>7023519</v>
+        <v>7023322</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3123,7 +3100,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3133,7 +3110,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3148,7 +3125,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3186,42 +3163,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133965188</v>
+        <v>133965147</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>99203</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3229,10 +3206,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490585</v>
+        <v>490433</v>
       </c>
       <c r="R22" t="n">
-        <v>7023147</v>
+        <v>7023417</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3264,7 +3241,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3274,12 +3251,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, rikligt spridda längs minst 6 meter på en granstam. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3288,37 +3260,13 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3336,10 +3284,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133965133</v>
+        <v>133965127</v>
       </c>
       <c r="B23" t="n">
-        <v>79359</v>
+        <v>58410</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3347,37 +3295,54 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490446</v>
+        <v>490366</v>
       </c>
       <c r="R23" t="n">
-        <v>7023313</v>
+        <v>7023424</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3409,7 +3374,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3419,7 +3384,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3428,7 +3393,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3437,24 +3401,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3472,37 +3421,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133965159</v>
+        <v>133965080</v>
       </c>
       <c r="B24" t="n">
-        <v>79359</v>
+        <v>99203</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3510,10 +3464,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490533</v>
+        <v>490455</v>
       </c>
       <c r="R24" t="n">
-        <v>7023322</v>
+        <v>7023418</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3545,7 +3499,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3555,7 +3509,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3570,27 +3524,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3608,27 +3542,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133965132</v>
+        <v>133965145</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>58349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3636,25 +3570,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490452</v>
+        <v>490443</v>
       </c>
       <c r="R25" t="n">
-        <v>7023297</v>
+        <v>7023398</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3686,7 +3632,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3696,12 +3642,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, färska, långt upp på en gran.</t>
+          <t>1 hane med sång i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3715,27 +3661,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3753,27 +3679,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133965081</v>
+        <v>133965040</v>
       </c>
       <c r="B26" t="n">
-        <v>57975</v>
+        <v>58349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3781,25 +3707,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490454</v>
+        <v>490083</v>
       </c>
       <c r="R26" t="n">
-        <v>7023418</v>
+        <v>7023533</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3831,7 +3769,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3841,12 +3779,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en döende gran. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3860,22 +3793,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3893,42 +3811,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133965134</v>
+        <v>133965031</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>101389</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3936,10 +3854,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490464</v>
+        <v>490134</v>
       </c>
       <c r="R27" t="n">
-        <v>7023330</v>
+        <v>7023468</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3971,7 +3889,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3981,12 +3899,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre och möjligen färska, från stambasen och några meter upp på en gran.</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3995,32 +3908,13 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4038,42 +3932,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133965131</v>
+        <v>133965111</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>101389</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4081,10 +3975,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490430</v>
+        <v>490303</v>
       </c>
       <c r="R28" t="n">
-        <v>7023332</v>
+        <v>7023488</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4116,7 +4010,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4126,12 +4020,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4140,32 +4029,13 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4183,10 +4053,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133965147</v>
+        <v>133965176</v>
       </c>
       <c r="B29" t="n">
-        <v>99203</v>
+        <v>98046</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4194,30 +4064,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -4226,10 +4092,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490433</v>
+        <v>490499</v>
       </c>
       <c r="R29" t="n">
-        <v>7023417</v>
+        <v>7023306</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4261,7 +4127,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4271,7 +4137,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4304,7 +4170,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133965080</v>
+        <v>133965166</v>
       </c>
       <c r="B30" t="n">
         <v>99203</v>
@@ -4332,25 +4198,37 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490455</v>
+        <v>490583</v>
       </c>
       <c r="R30" t="n">
-        <v>7023418</v>
+        <v>7023221</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4382,7 +4260,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4392,7 +4270,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4425,65 +4308,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133965127</v>
+        <v>133965072</v>
       </c>
       <c r="B31" t="n">
-        <v>58410</v>
+        <v>101389</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103001</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490366</v>
+        <v>490338</v>
       </c>
       <c r="R31" t="n">
-        <v>7023424</v>
+        <v>7023548</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4515,7 +4386,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4525,7 +4396,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4534,17 +4405,13 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4562,10 +4429,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133965145</v>
+        <v>133965170</v>
       </c>
       <c r="B32" t="n">
-        <v>58349</v>
+        <v>101389</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4573,54 +4440,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490443</v>
+        <v>490498</v>
       </c>
       <c r="R32" t="n">
-        <v>7023398</v>
+        <v>7023269</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4652,7 +4507,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4662,12 +4517,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>1 hane med sång i flerskiktad granskog.</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4676,12 +4526,13 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4699,42 +4550,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133965139</v>
+        <v>133965103</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>99181</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4742,10 +4601,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490413</v>
+        <v>490285</v>
       </c>
       <c r="R33" t="n">
-        <v>7023348</v>
+        <v>7023490</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4777,7 +4636,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4787,12 +4646,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, några meter upp på en granstam.</t>
+          <t>Minst 40 plantor och 1 vinterståndare inom ca 1 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4801,37 +4660,13 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4849,10 +4684,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133965186</v>
+        <v>133965148</v>
       </c>
       <c r="B34" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4860,31 +4695,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4892,10 +4722,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490556</v>
+        <v>490433</v>
       </c>
       <c r="R34" t="n">
-        <v>7023170</v>
+        <v>7023420</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4927,7 +4757,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4937,12 +4767,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en granstam. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4951,6 +4781,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4959,11 +4790,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ34" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4976,12 +4802,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4999,10 +4825,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133965040</v>
+        <v>133965105</v>
       </c>
       <c r="B35" t="n">
-        <v>58349</v>
+        <v>101389</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5010,54 +4836,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490083</v>
+        <v>490320</v>
       </c>
       <c r="R35" t="n">
-        <v>7023533</v>
+        <v>7023480</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5089,7 +4903,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5099,7 +4913,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5108,12 +4922,13 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5131,42 +4946,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133965031</v>
+        <v>133965086</v>
       </c>
       <c r="B36" t="n">
-        <v>101389</v>
+        <v>79359</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5174,10 +4984,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490134</v>
+        <v>490432</v>
       </c>
       <c r="R36" t="n">
-        <v>7023468</v>
+        <v>7023454</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5209,7 +5019,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5219,7 +5029,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5235,6 +5045,26 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5252,7 +5082,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133965111</v>
+        <v>133965056</v>
       </c>
       <c r="B37" t="n">
         <v>101389</v>
@@ -5284,7 +5114,7 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -5295,10 +5125,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490303</v>
+        <v>490193</v>
       </c>
       <c r="R37" t="n">
-        <v>7023488</v>
+        <v>7023617</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5330,7 +5160,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5340,7 +5170,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5373,42 +5203,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133965185</v>
+        <v>133965154</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>99203</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5416,10 +5246,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490555</v>
+        <v>490499</v>
       </c>
       <c r="R38" t="n">
-        <v>7023176</v>
+        <v>7023371</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5451,7 +5281,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5461,12 +5291,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5475,37 +5300,13 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5523,10 +5324,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133965166</v>
+        <v>133965097</v>
       </c>
       <c r="B39" t="n">
-        <v>99203</v>
+        <v>101389</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5534,54 +5335,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490583</v>
+        <v>490353</v>
       </c>
       <c r="R39" t="n">
-        <v>7023221</v>
+        <v>7023486</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5613,7 +5402,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5623,12 +5412,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta i barrblandskog.</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5661,49 +5445,65 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133965176</v>
+        <v>133965141</v>
       </c>
       <c r="B40" t="n">
-        <v>98046</v>
+        <v>99181</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490499</v>
+        <v>490416</v>
       </c>
       <c r="R40" t="n">
-        <v>7023306</v>
+        <v>7023409</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5735,7 +5535,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5745,7 +5545,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5778,7 +5583,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133965072</v>
+        <v>133965064</v>
       </c>
       <c r="B41" t="n">
         <v>101389</v>
@@ -5821,10 +5626,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490338</v>
+        <v>490309</v>
       </c>
       <c r="R41" t="n">
-        <v>7023548</v>
+        <v>7023606</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5856,7 +5661,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5866,7 +5671,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Blåsippa relativt allmänt förekommande här.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5899,10 +5709,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133965170</v>
+        <v>133965142</v>
       </c>
       <c r="B42" t="n">
-        <v>101389</v>
+        <v>99203</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5910,28 +5720,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -5942,10 +5752,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490498</v>
+        <v>490418</v>
       </c>
       <c r="R42" t="n">
-        <v>7023269</v>
+        <v>7023409</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5977,7 +5787,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5987,7 +5797,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6002,7 +5812,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6020,7 +5830,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133965148</v>
+        <v>133965156</v>
       </c>
       <c r="B43" t="n">
         <v>79359</v>
@@ -6058,10 +5868,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490433</v>
+        <v>490516</v>
       </c>
       <c r="R43" t="n">
-        <v>7023420</v>
+        <v>7023332</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6093,7 +5903,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6103,12 +5913,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gran i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6123,7 +5933,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6161,44 +5971,36 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133965103</v>
+        <v>133965121</v>
       </c>
       <c r="B44" t="n">
-        <v>99181</v>
+        <v>101389</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -6212,10 +6014,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490285</v>
+        <v>490327</v>
       </c>
       <c r="R44" t="n">
-        <v>7023490</v>
+        <v>7023388</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6247,7 +6049,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6257,12 +6059,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:42</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 40 plantor och 1 vinterståndare inom ca 1 m2 yta i barrblandskog.</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6295,10 +6092,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133965105</v>
+        <v>133965125</v>
       </c>
       <c r="B45" t="n">
-        <v>101389</v>
+        <v>58658</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6306,42 +6103,54 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490320</v>
+        <v>490397</v>
       </c>
       <c r="R45" t="n">
-        <v>7023480</v>
+        <v>7023379</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6373,7 +6182,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6383,7 +6192,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 1 hane med sång.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6392,7 +6206,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6416,37 +6229,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133965086</v>
+        <v>133965180</v>
       </c>
       <c r="B46" t="n">
-        <v>79359</v>
+        <v>101389</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6454,10 +6272,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490432</v>
+        <v>490500</v>
       </c>
       <c r="R46" t="n">
-        <v>7023454</v>
+        <v>7023226</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6489,7 +6307,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6499,7 +6317,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6514,27 +6332,12 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6552,42 +6355,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133965119</v>
+        <v>133965087</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>101389</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6595,10 +6398,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490335</v>
+        <v>490428</v>
       </c>
       <c r="R47" t="n">
-        <v>7023391</v>
+        <v>7023454</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6630,7 +6433,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6640,12 +6443,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6654,32 +6452,13 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6697,10 +6476,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133965190</v>
+        <v>133965099</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6708,31 +6487,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6740,10 +6514,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490603</v>
+        <v>490300</v>
       </c>
       <c r="R48" t="n">
-        <v>7023135</v>
+        <v>7023522</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6775,7 +6549,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6785,12 +6559,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, spridda längs flera meter på en granstam. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6799,6 +6568,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6807,11 +6577,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ48" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6824,12 +6589,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6847,10 +6612,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133965154</v>
+        <v>133965050</v>
       </c>
       <c r="B49" t="n">
-        <v>99203</v>
+        <v>101389</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6858,28 +6623,28 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -6890,10 +6655,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490499</v>
+        <v>490198</v>
       </c>
       <c r="R49" t="n">
-        <v>7023371</v>
+        <v>7023555</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6925,7 +6690,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6935,7 +6700,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6968,7 +6733,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133965064</v>
+        <v>133965112</v>
       </c>
       <c r="B50" t="n">
         <v>101389</v>
@@ -7011,10 +6776,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490309</v>
+        <v>490303</v>
       </c>
       <c r="R50" t="n">
-        <v>7023606</v>
+        <v>7023486</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7046,7 +6811,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7056,12 +6821,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Blåsippa relativt allmänt förekommande här.</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7077,6 +6837,11 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7094,36 +6859,44 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133965056</v>
+        <v>133965143</v>
       </c>
       <c r="B51" t="n">
-        <v>101389</v>
+        <v>99181</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7137,10 +6910,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490193</v>
+        <v>490432</v>
       </c>
       <c r="R51" t="n">
-        <v>7023617</v>
+        <v>7023411</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7172,7 +6945,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7182,7 +6955,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minst 33 plantor och 2 vinterståndare inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7197,7 +6975,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7215,65 +6993,52 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133965141</v>
+        <v>133965090</v>
       </c>
       <c r="B52" t="n">
-        <v>99181</v>
+        <v>80479</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490416</v>
+        <v>490385</v>
       </c>
       <c r="R52" t="n">
-        <v>7023409</v>
+        <v>7023452</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7305,7 +7070,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7315,12 +7080,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 25 plantor inom ca 1 m2 yta i granskog.</t>
+          <t>Enstaka bålar på en sliten klen sälg.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7335,7 +7100,27 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7353,42 +7138,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133965178</v>
+        <v>133965152</v>
       </c>
       <c r="B53" t="n">
-        <v>57975</v>
+        <v>101389</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7396,10 +7181,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490472</v>
+        <v>490481</v>
       </c>
       <c r="R53" t="n">
-        <v>7023283</v>
+        <v>7023372</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7431,7 +7216,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7441,12 +7226,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, några meter upp på en gran.</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7455,32 +7235,13 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7498,10 +7259,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133965097</v>
+        <v>133965151</v>
       </c>
       <c r="B54" t="n">
-        <v>101389</v>
+        <v>58349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7509,42 +7270,54 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490353</v>
+        <v>490484</v>
       </c>
       <c r="R54" t="n">
-        <v>7023486</v>
+        <v>7023377</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7576,7 +7349,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7586,7 +7359,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1 hane med sång i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7595,13 +7373,12 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7619,10 +7396,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133965203</v>
+        <v>133965161</v>
       </c>
       <c r="B55" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7630,46 +7407,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490642</v>
+        <v>490539</v>
       </c>
       <c r="R55" t="n">
-        <v>7023193</v>
+        <v>7023282</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7701,7 +7469,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7711,12 +7479,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en granstam.</t>
+          <t>Enstaka bålar på en gran.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7725,6 +7493,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7733,11 +7502,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ55" t="inlineStr">
         <is>
           <t>gran</t>
@@ -7750,12 +7514,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7773,10 +7537,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133965142</v>
+        <v>133965115</v>
       </c>
       <c r="B56" t="n">
-        <v>99203</v>
+        <v>101389</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7784,28 +7548,28 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -7816,10 +7580,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490418</v>
+        <v>490272</v>
       </c>
       <c r="R56" t="n">
-        <v>7023409</v>
+        <v>7023434</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7851,7 +7615,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7861,7 +7625,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7876,7 +7640,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7894,10 +7658,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133965156</v>
+        <v>133965188</v>
       </c>
       <c r="B57" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7905,26 +7669,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7932,10 +7701,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490516</v>
+        <v>490585</v>
       </c>
       <c r="R57" t="n">
-        <v>7023332</v>
+        <v>7023147</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7967,7 +7736,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7977,12 +7746,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På gran i flerskiktad granskog.</t>
+          <t>Ringhack, färska, rikligt spridda längs minst 6 meter på en granstam. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7991,13 +7760,17 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -8012,12 +7785,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8035,7 +7808,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133965137</v>
+        <v>133965134</v>
       </c>
       <c r="B58" t="n">
         <v>57975</v>
@@ -8068,7 +7841,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -8078,10 +7851,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490446</v>
+        <v>490464</v>
       </c>
       <c r="R58" t="n">
-        <v>7023318</v>
+        <v>7023330</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8113,7 +7886,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8123,12 +7896,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, några meter upp på en granstam.</t>
+          <t>Ringhack, äldre och möjligen färska, från stambasen och några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8142,12 +7915,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>Luckig barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -8185,27 +7953,27 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133965125</v>
+        <v>133965189</v>
       </c>
       <c r="B59" t="n">
-        <v>58658</v>
+        <v>57975</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103044</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -8213,37 +7981,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490397</v>
+        <v>490597</v>
       </c>
       <c r="R59" t="n">
-        <v>7023379</v>
+        <v>7023144</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8275,7 +8031,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8285,12 +8041,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Minst 1 hane med sång.</t>
+          <t>Ringhack, färska och äldre, några meter upp på en granstam. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8305,6 +8061,31 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8322,42 +8103,42 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133965121</v>
+        <v>133965136</v>
       </c>
       <c r="B60" t="n">
-        <v>101389</v>
+        <v>57975</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8365,10 +8146,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490327</v>
+        <v>490454</v>
       </c>
       <c r="R60" t="n">
-        <v>7023388</v>
+        <v>7023309</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8400,7 +8181,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8410,7 +8191,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8419,13 +8205,37 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8443,42 +8253,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133965180</v>
+        <v>133965130</v>
       </c>
       <c r="B61" t="n">
-        <v>101389</v>
+        <v>57975</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8486,10 +8296,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490500</v>
+        <v>490393</v>
       </c>
       <c r="R61" t="n">
-        <v>7023226</v>
+        <v>7023359</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8521,7 +8331,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8531,7 +8341,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, några meter upp på en gran. Sannolikt årsfärska ringhack från 2026.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8540,7 +8355,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -8552,6 +8366,26 @@
       <c r="AI61" t="inlineStr">
         <is>
           <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8569,7 +8403,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133965036</v>
+        <v>133965204</v>
       </c>
       <c r="B62" t="n">
         <v>57975</v>
@@ -8602,20 +8436,24 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490094</v>
+        <v>490639</v>
       </c>
       <c r="R62" t="n">
-        <v>7023484</v>
+        <v>7023193</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8647,7 +8485,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8657,12 +8495,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran. Kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, färska, spridda längs flera meter på en granstam. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8676,7 +8514,12 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -8714,42 +8557,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133965087</v>
+        <v>133965182</v>
       </c>
       <c r="B63" t="n">
-        <v>101389</v>
+        <v>57975</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8757,10 +8600,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490428</v>
+        <v>490512</v>
       </c>
       <c r="R63" t="n">
-        <v>7023454</v>
+        <v>7023205</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8792,7 +8635,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8802,7 +8645,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, några meter upp på en gran. På/kring fyndplatsen finns stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8811,13 +8659,37 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8835,7 +8707,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133965184</v>
+        <v>133965183</v>
       </c>
       <c r="B64" t="n">
         <v>57975</v>
@@ -8868,7 +8740,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -8878,10 +8750,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490553</v>
+        <v>490539</v>
       </c>
       <c r="R64" t="n">
-        <v>7023183</v>
+        <v>7023187</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8913,7 +8785,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8923,12 +8795,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en klen gran. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, några meter upp på en gran. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8985,7 +8857,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133965138</v>
+        <v>133965129</v>
       </c>
       <c r="B65" t="n">
         <v>57975</v>
@@ -9028,10 +8900,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490422</v>
+        <v>490383</v>
       </c>
       <c r="R65" t="n">
-        <v>7023345</v>
+        <v>7023375</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9063,7 +8935,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9073,12 +8945,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran.</t>
+          <t>Ringhack, färska, på en klen gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9130,10 +9002,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133965099</v>
+        <v>133965132</v>
       </c>
       <c r="B66" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9141,26 +9013,31 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9168,10 +9045,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>490300</v>
+        <v>490452</v>
       </c>
       <c r="R66" t="n">
-        <v>7023522</v>
+        <v>7023297</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9203,7 +9080,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9213,7 +9090,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, långt upp på en gran.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9222,7 +9104,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -9243,12 +9124,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9266,7 +9147,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133965033</v>
+        <v>133965081</v>
       </c>
       <c r="B67" t="n">
         <v>57975</v>
@@ -9299,7 +9180,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -9309,10 +9190,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490113</v>
+        <v>490454</v>
       </c>
       <c r="R67" t="n">
-        <v>7023469</v>
+        <v>7023418</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9344,7 +9225,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9354,12 +9235,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran. Kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, på en döende gran. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9373,7 +9254,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -9386,14 +9267,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9411,42 +9287,42 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133965050</v>
+        <v>133965131</v>
       </c>
       <c r="B68" t="n">
-        <v>101389</v>
+        <v>57975</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9454,10 +9330,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490198</v>
+        <v>490430</v>
       </c>
       <c r="R68" t="n">
-        <v>7023555</v>
+        <v>7023332</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9489,7 +9365,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9499,7 +9375,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9508,13 +9389,32 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9532,7 +9432,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133965123</v>
+        <v>133965139</v>
       </c>
       <c r="B69" t="n">
         <v>57975</v>
@@ -9575,10 +9475,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490364</v>
+        <v>490413</v>
       </c>
       <c r="R69" t="n">
-        <v>7023364</v>
+        <v>7023348</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9610,7 +9510,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9620,12 +9520,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en gran.</t>
+          <t>Ringhack, färska och äldre, några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9682,42 +9582,42 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133965112</v>
+        <v>133965186</v>
       </c>
       <c r="B70" t="n">
-        <v>101389</v>
+        <v>57975</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9725,10 +9625,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490303</v>
+        <v>490556</v>
       </c>
       <c r="R70" t="n">
-        <v>7023486</v>
+        <v>7023170</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9760,7 +9660,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9770,7 +9670,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, några meter upp på en granstam. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9779,7 +9684,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -9791,6 +9695,26 @@
       <c r="AI70" t="inlineStr">
         <is>
           <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9808,7 +9732,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133965136</v>
+        <v>133965185</v>
       </c>
       <c r="B71" t="n">
         <v>57975</v>
@@ -9851,10 +9775,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490454</v>
+        <v>490555</v>
       </c>
       <c r="R71" t="n">
-        <v>7023309</v>
+        <v>7023176</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9886,7 +9810,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9896,12 +9820,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en granstam.</t>
+          <t>Ringhack, färska, på en gran. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9958,7 +9882,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133965189</v>
+        <v>133965190</v>
       </c>
       <c r="B72" t="n">
         <v>57975</v>
@@ -9991,7 +9915,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -10001,10 +9925,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490597</v>
+        <v>490603</v>
       </c>
       <c r="R72" t="n">
-        <v>7023144</v>
+        <v>7023135</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -10036,7 +9960,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10046,12 +9970,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, några meter upp på en granstam. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, spridda längs flera meter på en granstam. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10108,39 +10032,40 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133965090</v>
+        <v>133965119</v>
       </c>
       <c r="B73" t="n">
-        <v>80479</v>
+        <v>57975</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -10150,10 +10075,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490385</v>
+        <v>490335</v>
       </c>
       <c r="R73" t="n">
-        <v>7023452</v>
+        <v>7023391</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10185,7 +10110,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10195,12 +10120,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en sliten klen sälg.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10209,7 +10134,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -10220,22 +10144,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10253,7 +10177,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133965204</v>
+        <v>133965203</v>
       </c>
       <c r="B74" t="n">
         <v>57975</v>
@@ -10300,7 +10224,7 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490639</v>
+        <v>490642</v>
       </c>
       <c r="R74" t="n">
         <v>7023193</v>
@@ -10335,7 +10259,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10345,12 +10269,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack, färska, spridda längs flera meter på en granstam. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, färska, några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10407,7 +10331,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133965130</v>
+        <v>133965178</v>
       </c>
       <c r="B75" t="n">
         <v>57975</v>
@@ -10440,7 +10364,7 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -10450,10 +10374,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490393</v>
+        <v>490472</v>
       </c>
       <c r="R75" t="n">
-        <v>7023359</v>
+        <v>7023283</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10485,7 +10409,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10495,12 +10419,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en gran. Sannolikt årsfärska ringhack från 2026.</t>
+          <t>Ringhack, äldre, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10515,11 +10439,6 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -10557,50 +10476,42 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133965143</v>
+        <v>133965137</v>
       </c>
       <c r="B76" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10608,10 +10519,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>490432</v>
+        <v>490446</v>
       </c>
       <c r="R76" t="n">
-        <v>7023411</v>
+        <v>7023318</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10643,7 +10554,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10653,12 +10564,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Minst 33 plantor och 2 vinterståndare inom ca 1 m2 yta i granskog.</t>
+          <t>Ringhack (savhack), färska, några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10667,13 +10578,37 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Luckig barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10691,27 +10626,27 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133965151</v>
+        <v>133965036</v>
       </c>
       <c r="B77" t="n">
-        <v>58349</v>
+        <v>57975</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -10719,37 +10654,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>490484</v>
+        <v>490094</v>
       </c>
       <c r="R77" t="n">
-        <v>7023377</v>
+        <v>7023484</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10781,7 +10704,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10791,12 +10714,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>1 hane med sång i flerskiktad äldre granskog.</t>
+          <t>Ringhack, äldre, på en gran. Kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10811,6 +10734,26 @@
       <c r="AH77" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10828,10 +10771,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133965161</v>
+        <v>133965184</v>
       </c>
       <c r="B78" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10839,26 +10782,31 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10866,10 +10814,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>490539</v>
+        <v>490553</v>
       </c>
       <c r="R78" t="n">
-        <v>7023282</v>
+        <v>7023183</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10901,7 +10849,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10911,12 +10859,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en gran.</t>
+          <t>Ringhack, färska, på en klen gran. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10925,7 +10873,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -10934,6 +10881,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ78" t="inlineStr">
         <is>
           <t>gran</t>
@@ -10946,12 +10898,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10969,42 +10921,42 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133965115</v>
+        <v>133965138</v>
       </c>
       <c r="B79" t="n">
-        <v>101389</v>
+        <v>57975</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -11012,10 +10964,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>490272</v>
+        <v>490422</v>
       </c>
       <c r="R79" t="n">
-        <v>7023434</v>
+        <v>7023345</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -11047,7 +10999,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11057,7 +11009,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11066,13 +11023,32 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11090,42 +11066,42 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133965152</v>
+        <v>133965033</v>
       </c>
       <c r="B80" t="n">
-        <v>101389</v>
+        <v>57975</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -11133,10 +11109,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>490481</v>
+        <v>490113</v>
       </c>
       <c r="R80" t="n">
-        <v>7023372</v>
+        <v>7023469</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11168,7 +11144,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11178,7 +11154,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran. Kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11187,13 +11168,32 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11211,7 +11211,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133965187</v>
+        <v>133965123</v>
       </c>
       <c r="B81" t="n">
         <v>57975</v>
@@ -11244,7 +11244,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -11254,10 +11254,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>490581</v>
+        <v>490364</v>
       </c>
       <c r="R81" t="n">
-        <v>7023153</v>
+        <v>7023364</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11289,7 +11289,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11299,12 +11299,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, spridda längs flera meter på en granstam. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, färska, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
@@ -11361,7 +11361,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133965182</v>
+        <v>133965187</v>
       </c>
       <c r="B82" t="n">
         <v>57975</v>
@@ -11394,7 +11394,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -11404,10 +11404,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>490512</v>
+        <v>490581</v>
       </c>
       <c r="R82" t="n">
-        <v>7023205</v>
+        <v>7023153</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11449,12 +11449,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en gran. På/kring fyndplatsen finns stående död ved som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, spridda längs flera meter på en granstam. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">

--- a/artfynd/A 56647-2025 artfynd.xlsx
+++ b/artfynd/A 56647-2025 artfynd.xlsx
@@ -1959,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133965102</v>
+        <v>133965075</v>
       </c>
       <c r="B13" t="n">
-        <v>99098</v>
+        <v>101396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,36 +1970,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2010,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490285</v>
+        <v>490371</v>
       </c>
       <c r="R13" t="n">
-        <v>7023491</v>
+        <v>7023521</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2045,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2055,12 +2047,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:42</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 1 planta i barrblandskog.</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2093,10 +2080,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133965075</v>
+        <v>133965102</v>
       </c>
       <c r="B14" t="n">
-        <v>101389</v>
+        <v>99105</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,28 +2091,36 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -2136,10 +2131,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490371</v>
+        <v>490285</v>
       </c>
       <c r="R14" t="n">
-        <v>7023521</v>
+        <v>7023491</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2171,7 +2166,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2181,7 +2176,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 1 planta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2214,42 +2214,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133965162</v>
+        <v>133965116</v>
       </c>
       <c r="B15" t="n">
-        <v>99203</v>
+        <v>79366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2257,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490592</v>
+        <v>490332</v>
       </c>
       <c r="R15" t="n">
-        <v>7023284</v>
+        <v>7023439</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2292,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2302,7 +2297,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2318,6 +2318,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2335,61 +2355,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133965201</v>
+        <v>133965162</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>99210</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490629</v>
+        <v>490592</v>
       </c>
       <c r="R16" t="n">
-        <v>7023175</v>
+        <v>7023284</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2421,7 +2433,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2431,12 +2443,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gammalt bohål på 1,6 meters höjd med ca 40-45 mm i diameter i en ca 3 meter hög granhögstubbe. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2445,37 +2452,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2493,10 +2476,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133965116</v>
+        <v>133965201</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2504,37 +2487,50 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490332</v>
+        <v>490629</v>
       </c>
       <c r="R17" t="n">
-        <v>7023439</v>
+        <v>7023175</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2566,7 +2562,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2576,12 +2572,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gran i barrblandskog.</t>
+          <t>Gammalt bohål på 1,6 meters höjd med ca 40-45 mm i diameter i en ca 3 meter hög granhögstubbe. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2590,7 +2586,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2599,6 +2594,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ17" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2611,12 +2611,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2637,7 +2637,7 @@
         <v>133965173</v>
       </c>
       <c r="B18" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>133965073</v>
       </c>
       <c r="B19" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>133965133</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>133965159</v>
       </c>
       <c r="B21" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3163,10 +3163,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133965147</v>
+        <v>133965080</v>
       </c>
       <c r="B22" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490433</v>
+        <v>490455</v>
       </c>
       <c r="R22" t="n">
-        <v>7023417</v>
+        <v>7023418</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3284,65 +3284,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133965127</v>
+        <v>133965147</v>
       </c>
       <c r="B23" t="n">
-        <v>58410</v>
+        <v>99210</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103001</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490366</v>
+        <v>490433</v>
       </c>
       <c r="R23" t="n">
-        <v>7023424</v>
+        <v>7023417</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3374,7 +3362,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3384,7 +3372,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3393,17 +3381,13 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3421,10 +3405,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133965080</v>
+        <v>133965145</v>
       </c>
       <c r="B24" t="n">
-        <v>99203</v>
+        <v>58349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3432,42 +3416,54 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490455</v>
+        <v>490443</v>
       </c>
       <c r="R24" t="n">
-        <v>7023418</v>
+        <v>7023398</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3499,7 +3495,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3509,7 +3505,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1 hane med sång i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3518,13 +3519,12 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3542,32 +3542,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133965145</v>
+        <v>133965127</v>
       </c>
       <c r="B25" t="n">
-        <v>58349</v>
+        <v>58410</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490443</v>
+        <v>490366</v>
       </c>
       <c r="R25" t="n">
-        <v>7023398</v>
+        <v>7023424</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3642,12 +3642,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>1 hane med sång i flerskiktad granskog.</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3661,7 +3656,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133965040</v>
+        <v>133965031</v>
       </c>
       <c r="B26" t="n">
-        <v>58349</v>
+        <v>101396</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3690,54 +3690,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490083</v>
+        <v>490134</v>
       </c>
       <c r="R26" t="n">
-        <v>7023533</v>
+        <v>7023468</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3769,7 +3757,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3779,7 +3767,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3788,6 +3776,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3811,10 +3800,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133965031</v>
+        <v>133965040</v>
       </c>
       <c r="B27" t="n">
-        <v>101389</v>
+        <v>58349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3822,42 +3811,54 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490134</v>
+        <v>490083</v>
       </c>
       <c r="R27" t="n">
-        <v>7023468</v>
+        <v>7023533</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3889,7 +3890,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3899,7 +3900,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3908,7 +3909,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>133965111</v>
       </c>
       <c r="B28" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>133965176</v>
       </c>
       <c r="B29" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>133965166</v>
       </c>
       <c r="B30" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4308,10 +4308,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133965072</v>
+        <v>133965170</v>
       </c>
       <c r="B31" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4351,10 +4351,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490338</v>
+        <v>490498</v>
       </c>
       <c r="R31" t="n">
-        <v>7023548</v>
+        <v>7023269</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4429,10 +4429,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133965170</v>
+        <v>133965072</v>
       </c>
       <c r="B32" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4472,10 +4472,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490498</v>
+        <v>490338</v>
       </c>
       <c r="R32" t="n">
-        <v>7023269</v>
+        <v>7023548</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4553,7 +4553,7 @@
         <v>133965103</v>
       </c>
       <c r="B33" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>133965148</v>
       </c>
       <c r="B34" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4825,42 +4825,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133965105</v>
+        <v>133965086</v>
       </c>
       <c r="B35" t="n">
-        <v>101389</v>
+        <v>79366</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4868,10 +4863,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490320</v>
+        <v>490432</v>
       </c>
       <c r="R35" t="n">
-        <v>7023480</v>
+        <v>7023454</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4903,7 +4898,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4913,7 +4908,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4928,7 +4923,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4946,37 +4961,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133965086</v>
+        <v>133965105</v>
       </c>
       <c r="B36" t="n">
-        <v>79359</v>
+        <v>101396</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4984,10 +5004,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490432</v>
+        <v>490320</v>
       </c>
       <c r="R36" t="n">
-        <v>7023454</v>
+        <v>7023480</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5019,7 +5039,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5029,7 +5049,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5044,27 +5064,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133965056</v>
+        <v>133965097</v>
       </c>
       <c r="B37" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490193</v>
+        <v>490353</v>
       </c>
       <c r="R37" t="n">
-        <v>7023617</v>
+        <v>7023486</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5203,10 +5203,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133965154</v>
+        <v>133965056</v>
       </c>
       <c r="B38" t="n">
-        <v>99203</v>
+        <v>101396</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5214,28 +5214,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5246,10 +5246,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490499</v>
+        <v>490193</v>
       </c>
       <c r="R38" t="n">
-        <v>7023371</v>
+        <v>7023617</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5324,53 +5324,65 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133965097</v>
+        <v>133965141</v>
       </c>
       <c r="B39" t="n">
-        <v>101389</v>
+        <v>99188</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490353</v>
+        <v>490416</v>
       </c>
       <c r="R39" t="n">
-        <v>7023486</v>
+        <v>7023409</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5402,7 +5414,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5412,7 +5424,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor inom ca 1 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5427,7 +5444,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5445,65 +5462,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133965141</v>
+        <v>133965064</v>
       </c>
       <c r="B40" t="n">
-        <v>99181</v>
+        <v>101396</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490416</v>
+        <v>490309</v>
       </c>
       <c r="R40" t="n">
-        <v>7023409</v>
+        <v>7023606</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5535,7 +5540,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5545,12 +5550,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Minst 25 plantor inom ca 1 m2 yta i granskog.</t>
+          <t>Blåsippa relativt allmänt förekommande här.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5565,7 +5570,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5583,10 +5588,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133965064</v>
+        <v>133965154</v>
       </c>
       <c r="B41" t="n">
-        <v>101389</v>
+        <v>99210</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5594,28 +5599,28 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -5626,10 +5631,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490309</v>
+        <v>490499</v>
       </c>
       <c r="R41" t="n">
-        <v>7023606</v>
+        <v>7023371</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5661,7 +5666,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5671,12 +5676,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Blåsippa relativt allmänt förekommande här.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5712,7 +5712,7 @@
         <v>133965142</v>
       </c>
       <c r="B42" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>133965156</v>
       </c>
       <c r="B43" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5971,10 +5971,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133965121</v>
+        <v>133965180</v>
       </c>
       <c r="B44" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490327</v>
+        <v>490500</v>
       </c>
       <c r="R44" t="n">
-        <v>7023388</v>
+        <v>7023226</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6049,7 +6049,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6075,6 +6075,11 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6229,10 +6234,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133965180</v>
+        <v>133965121</v>
       </c>
       <c r="B46" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6272,10 +6277,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490500</v>
+        <v>490327</v>
       </c>
       <c r="R46" t="n">
-        <v>7023226</v>
+        <v>7023388</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6307,7 +6312,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6317,7 +6322,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6333,11 +6338,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6358,7 +6358,7 @@
         <v>133965087</v>
       </c>
       <c r="B47" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>133965099</v>
       </c>
       <c r="B48" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>133965050</v>
       </c>
       <c r="B49" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>133965112</v>
       </c>
       <c r="B50" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>133965143</v>
       </c>
       <c r="B51" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>133965090</v>
       </c>
       <c r="B52" t="n">
-        <v>80479</v>
+        <v>80486</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>133965152</v>
       </c>
       <c r="B53" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7259,10 +7259,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133965151</v>
+        <v>133965115</v>
       </c>
       <c r="B54" t="n">
-        <v>58349</v>
+        <v>101396</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7270,54 +7270,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490484</v>
+        <v>490272</v>
       </c>
       <c r="R54" t="n">
-        <v>7023377</v>
+        <v>7023434</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7349,7 +7337,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7359,12 +7347,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>1 hane med sång i flerskiktad äldre granskog.</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7373,12 +7356,13 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7396,48 +7380,65 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133965161</v>
+        <v>133965151</v>
       </c>
       <c r="B55" t="n">
-        <v>79359</v>
+        <v>58349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490539</v>
+        <v>490484</v>
       </c>
       <c r="R55" t="n">
-        <v>7023282</v>
+        <v>7023377</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7469,7 +7470,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7479,12 +7480,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en gran.</t>
+          <t>1 hane med sång i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7493,33 +7494,12 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7537,42 +7517,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133965115</v>
+        <v>133965161</v>
       </c>
       <c r="B56" t="n">
-        <v>101389</v>
+        <v>79366</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7580,10 +7555,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490272</v>
+        <v>490539</v>
       </c>
       <c r="R56" t="n">
-        <v>7023434</v>
+        <v>7023282</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7615,7 +7590,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7625,7 +7600,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7641,6 +7621,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7953,7 +7953,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133965189</v>
+        <v>133965136</v>
       </c>
       <c r="B59" t="n">
         <v>57975</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490597</v>
+        <v>490454</v>
       </c>
       <c r="R59" t="n">
-        <v>7023144</v>
+        <v>7023309</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8041,12 +8041,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, några meter upp på en granstam. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, färska, några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8103,7 +8103,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133965136</v>
+        <v>133965189</v>
       </c>
       <c r="B60" t="n">
         <v>57975</v>
@@ -8146,10 +8146,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490454</v>
+        <v>490597</v>
       </c>
       <c r="R60" t="n">
-        <v>7023309</v>
+        <v>7023144</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en granstam.</t>
+          <t>Ringhack, färska och äldre, några meter upp på en granstam. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8253,7 +8253,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133965130</v>
+        <v>133965204</v>
       </c>
       <c r="B61" t="n">
         <v>57975</v>
@@ -8289,17 +8289,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490393</v>
+        <v>490639</v>
       </c>
       <c r="R61" t="n">
-        <v>7023359</v>
+        <v>7023193</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8331,7 +8335,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8341,12 +8345,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en gran. Sannolikt årsfärska ringhack från 2026.</t>
+          <t>Ringhack, färska, spridda längs flera meter på en granstam. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8403,7 +8407,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133965204</v>
+        <v>133965130</v>
       </c>
       <c r="B62" t="n">
         <v>57975</v>
@@ -8439,21 +8443,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490639</v>
+        <v>490393</v>
       </c>
       <c r="R62" t="n">
-        <v>7023193</v>
+        <v>7023359</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8485,7 +8485,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack, färska, spridda längs flera meter på en granstam. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, färska, några meter upp på en gran. Sannolikt årsfärska ringhack från 2026.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9002,7 +9002,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133965132</v>
+        <v>133965081</v>
       </c>
       <c r="B66" t="n">
         <v>57975</v>
@@ -9035,7 +9035,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -9045,10 +9045,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>490452</v>
+        <v>490454</v>
       </c>
       <c r="R66" t="n">
-        <v>7023297</v>
+        <v>7023418</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9080,7 +9080,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9090,12 +9090,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack, färska, långt upp på en gran.</t>
+          <t>Ringhack, äldre, på en döende gran. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9122,14 +9122,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9147,7 +9142,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133965081</v>
+        <v>133965132</v>
       </c>
       <c r="B67" t="n">
         <v>57975</v>
@@ -9180,7 +9175,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -9190,10 +9185,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490454</v>
+        <v>490452</v>
       </c>
       <c r="R67" t="n">
-        <v>7023418</v>
+        <v>7023297</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9225,7 +9220,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9235,12 +9230,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en döende gran. På/kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, färska, långt upp på en gran.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9267,9 +9262,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9882,7 +9882,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133965190</v>
+        <v>133965119</v>
       </c>
       <c r="B72" t="n">
         <v>57975</v>
@@ -9915,7 +9915,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -9925,10 +9925,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490603</v>
+        <v>490335</v>
       </c>
       <c r="R72" t="n">
-        <v>7023135</v>
+        <v>7023391</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9970,12 +9970,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, spridda längs flera meter på en granstam. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9990,11 +9990,6 @@
       <c r="AH72" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -10032,7 +10027,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133965119</v>
+        <v>133965190</v>
       </c>
       <c r="B73" t="n">
         <v>57975</v>
@@ -10065,7 +10060,7 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -10075,10 +10070,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490335</v>
+        <v>490603</v>
       </c>
       <c r="R73" t="n">
-        <v>7023391</v>
+        <v>7023135</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10110,7 +10105,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10120,12 +10115,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, spridda längs flera meter på en granstam. Kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10140,6 +10135,11 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -10177,7 +10177,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133965203</v>
+        <v>133965178</v>
       </c>
       <c r="B74" t="n">
         <v>57975</v>
@@ -10210,24 +10210,20 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490642</v>
+        <v>490472</v>
       </c>
       <c r="R74" t="n">
-        <v>7023193</v>
+        <v>7023283</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10259,7 +10255,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10269,12 +10265,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack, färska, några meter upp på en granstam.</t>
+          <t>Ringhack, äldre, några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10289,11 +10285,6 @@
       <c r="AH74" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -10331,7 +10322,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133965178</v>
+        <v>133965203</v>
       </c>
       <c r="B75" t="n">
         <v>57975</v>
@@ -10364,20 +10355,24 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ljungtorpet NV, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490472</v>
+        <v>490642</v>
       </c>
       <c r="R75" t="n">
-        <v>7023283</v>
+        <v>7023193</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10409,7 +10404,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10419,12 +10414,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, några meter upp på en gran.</t>
+          <t>Ringhack, färska, några meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10439,6 +10434,11 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -10921,7 +10921,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133965138</v>
+        <v>133965033</v>
       </c>
       <c r="B79" t="n">
         <v>57975</v>
@@ -10964,10 +10964,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>490422</v>
+        <v>490113</v>
       </c>
       <c r="R79" t="n">
-        <v>7023345</v>
+        <v>7023469</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran.</t>
+          <t>Ringhack, färska och äldre, på en gran. Kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -11066,7 +11066,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133965033</v>
+        <v>133965138</v>
       </c>
       <c r="B80" t="n">
         <v>57975</v>
@@ -11109,10 +11109,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>490113</v>
+        <v>490422</v>
       </c>
       <c r="R80" t="n">
-        <v>7023469</v>
+        <v>7023345</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran. Kring fyndplatsen finns stående död ved som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">

--- a/artfynd/A 56647-2025 artfynd.xlsx
+++ b/artfynd/A 56647-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY107"/>
+  <dimension ref="A1:AZ107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113230947</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965046</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965070</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965076</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965094</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1355,6 +1385,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965106</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1477,6 +1512,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965110</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1594,6 +1634,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965120</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1716,6 +1761,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965171</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1833,6 +1883,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965174</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1955,6 +2010,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965179</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2072,6 +2132,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965193</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2194,6 +2259,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965197</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2296,6 +2366,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180053</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2398,6 +2473,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180054</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2500,6 +2580,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180055</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2631,6 +2716,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180056</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2733,6 +2823,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180057</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2835,6 +2930,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180058</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2971,6 +3071,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965073</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3107,6 +3212,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965086</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3243,6 +3353,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965099</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3384,6 +3499,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965116</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3520,6 +3640,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965133</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3661,6 +3786,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965148</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3802,6 +3932,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965156</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3938,6 +4073,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965159</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4079,6 +4219,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965161</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4224,6 +4369,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965090</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4359,6 +4509,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180010</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4494,6 +4649,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180011</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4629,6 +4789,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180012</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4764,6 +4929,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180013</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4909,6 +5079,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965033</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5054,6 +5229,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965036</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5194,6 +5374,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965081</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5339,6 +5524,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965119</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5489,6 +5679,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965123</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5634,6 +5829,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965129</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5784,6 +5984,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965130</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5929,6 +6134,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965131</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6074,6 +6284,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965132</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6219,6 +6434,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965134</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6369,6 +6589,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965136</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6519,6 +6744,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965137</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6664,6 +6894,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965138</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6814,6 +7049,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965139</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6959,6 +7199,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965178</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7109,6 +7354,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965182</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7259,6 +7509,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965183</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7409,6 +7664,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965184</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7559,6 +7819,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965185</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7709,6 +7974,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965186</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7859,6 +8129,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965187</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8009,6 +8284,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965188</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8159,6 +8439,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965189</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8309,6 +8594,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965190</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8467,6 +8757,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965201</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8621,6 +8916,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965203</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8775,6 +9075,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965204</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8912,6 +9217,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965127</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -9044,6 +9354,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965040</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -9181,6 +9496,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965145</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -9318,6 +9638,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965151</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9455,6 +9780,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965125</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9589,6 +9919,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965102</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9695,6 +10030,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131914</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9816,6 +10156,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965084</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9950,6 +10295,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965103</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -10088,6 +10438,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965141</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -10222,6 +10577,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965143</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -10339,6 +10699,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965176</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -10460,6 +10825,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965080</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -10581,6 +10951,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965142</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -10702,6 +11077,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965147</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10823,6 +11203,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965154</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10944,6 +11329,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965162</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -11082,6 +11472,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965166</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -11188,6 +11583,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131915</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -11309,6 +11709,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965031</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -11430,6 +11835,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965050</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -11551,6 +11961,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965056</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -11677,6 +12092,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965064</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -11798,6 +12218,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965072</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -11919,6 +12344,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965075</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -12040,6 +12470,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965087</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -12161,6 +12596,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965097</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -12282,6 +12722,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965105</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -12403,6 +12848,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965111</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -12529,6 +12979,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965112</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -12650,6 +13105,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965115</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -12771,6 +13231,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965121</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -12892,6 +13357,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965152</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -13013,6 +13483,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965170</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -13134,6 +13609,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965173</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -13260,6 +13740,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965180</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -13386,6 +13871,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965155</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -13507,6 +13997,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965063</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -13628,6 +14123,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965069</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -13754,6 +14254,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965108</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -13876,6 +14381,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965027</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -13998,6 +14508,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965043</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -14120,6 +14635,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965048</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -14246,6 +14766,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965067</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -14368,6 +14893,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965104</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -14490,8 +15020,121 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965113</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>